--- a/www/download/COUNTRY.PRT.rpPE.xlsx
+++ b/www/download/COUNTRY.PRT.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.753131128393005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.769213022381593</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.872996442622493</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.897054046108829</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.938262390237803</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.08271976526432</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.11656986352008</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1.05752963778797</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.884017002857388</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.803923182519938</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803793926327915</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.796431997418625</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.729660723050932</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.679902078434333</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948696077396</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.531</t>
+          <t>0.00460759300288438</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>-0.0221637460095382</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.728</t>
+          <t>-0.0145444443931968</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>-0.0679401692210315</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.927</t>
+          <t>-0.0369737386468089</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>0.052044752693996</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.121</t>
+          <t>0.0275534179460526</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.151</t>
+          <t>-0.0422089979926343</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5.122</t>
+          <t>0.0268883887570912</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.117</t>
+          <t>-0.168677237941167</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>-0.164238151440836</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.201</t>
+          <t>-0.0925011485484414</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5.198</t>
+          <t>-0.0744211561848375</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>-0.0716152329726454</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.053</t>
+          <t>-0.073308746534666</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.576</t>
+          <t>-0.0628749567318434</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.618</t>
+          <t>-0.105291181353932</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>-0.101509856006793</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>-0.161714059864744</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.923</t>
+          <t>-0.109668135087112</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>-0.0327423509216774</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-0.069280568188712</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>-0.129258140890364</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>-0.00219623315197059</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.117</t>
+          <t>-0.25303496915238</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>-0.241502063285063</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>-0.19667178266483</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.375</t>
+          <t>-0.184320480430349</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.396</t>
+          <t>-0.194898434284248</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.314</t>
+          <t>-0.203692223055932</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8693.292</t>
+          <t>-0.533873062559393</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8720.653</t>
+          <t>-0.544446100868626</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8753.428</t>
+          <t>-0.541519812880807</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8907.131</t>
+          <t>-0.590026185786896</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9115.373</t>
+          <t>-0.579688837883524</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9296.705</t>
+          <t>-0.563928190090948</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9445.794</t>
+          <t>-0.578735421098969</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9496.836</t>
+          <t>-0.603092353578459</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9343.179</t>
+          <t>-0.682022700139416</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9429.324</t>
+          <t>-0.644913507677004</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9396.913</t>
+          <t>-0.631416714571954</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9539.606</t>
+          <t>-0.613204898250128</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>9588.836</t>
+          <t>-0.598454781108786</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>9552.777</t>
+          <t>-0.592817544359871</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9196.084</t>
+          <t>-0.590178814135316</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6769.189</t>
+          <t>25026464078.403</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6753.915</t>
+          <t>24396020228.7963</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6802.734</t>
+          <t>22448514346.0178</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6949.965</t>
+          <t>24594121165.5266</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7170.217</t>
+          <t>25338936353.5467</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7306.097</t>
+          <t>28348910493.2032</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7399.159</t>
+          <t>28633455709.6609</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7507.101</t>
+          <t>27691654434.4998</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7368.323</t>
+          <t>26444069870.3533</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7502.137</t>
+          <t>29269044301.0462</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7523.578</t>
+          <t>28118264306.7387</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7933.461</t>
+          <t>28295031781.9657</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7984.655</t>
+          <t>28217021531.9753</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7978.693</t>
+          <t>28422788949.7459</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7814.953</t>
+          <t>22826135569.0302</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>18760369287.3413</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>19254199897.0224</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>19023402006.0099</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>21388730623.304</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>21761231203.2949</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>21417008017.6699</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>22540287922.5308</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>24377232104.7977</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>25968749270.4443</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>28500544066.203</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>27807613443.5877</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>27662597197.0255</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>26409341145.4127</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>26016539785.5522</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>26006192576.9165</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>4293682.97561846</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>3973434.54762207</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>3911091.39538738</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>4149881.20907847</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>4336960.14130884</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>5043472.55227923</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>5057495.52781166</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>4587753.73579828</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>3709948.23711223</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>3516218.6031372</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>3253320.89208858</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>2974250.05309915</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2543353.4684079</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>2338564.09108107</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>2065577.05341964</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>31450.4636141377</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>31547.4527963762</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>30061.3974242016</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>28745.1483390372</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>30372.0823871641</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>31172.902640038</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>30462.1764687723</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>31013.9674441628</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>34180.4386853597</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>38501.4001813686</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>40992.299259413</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>44934.334473766</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>51461.6679932652</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>57136.27045065</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>53209.7565647891</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>82572.9447620218</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>81426.2405183095</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>73305.2525773091</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>76194.5884534344</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>79474.3619187831</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>86504.720966267</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>84282.1541427681</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>83686.5141767204</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>92651.9961518827</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>106530.129067465</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>110887.694020923</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>118652.725391722</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>139863.716646283</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>160076.811105564</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>118421.879671345</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>-0.325013042241723</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>-0.341235561621565</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>-0.346433136854004</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>-0.40861489260427</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>-0.378643348063977</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>-0.332457280563238</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>-0.34998829992532</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>-0.387684903137683</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>-0.442273925490204</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>-0.438887642743554</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>-0.422413167125913</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>-0.380842454518255</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>-0.367695693094844</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>-0.362075713099918</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>-0.349367169278537</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>17731.4246456308</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>18615.5934765216</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>17439.6391239375</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>18170.0777138217</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>18623.7065760445</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>18155.4086054125</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>18466.7562704419</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>20533.3261419113</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>25315.7365269341</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>28985.3787072453</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>30153.6234109167</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>34436.3887548414</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>40460.3207052331</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>55530.5518496543</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.753131128393005</t>
+          <t>5246.48170684637</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769213022381593</t>
+          <t>5321.92705630958</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.872996442622493</t>
+          <t>5109.0108784772</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.897054046108829</t>
+          <t>5567.95195067008</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262390237803</t>
+          <t>5546.52373025818</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976526432</t>
+          <t>5351.4424971065</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986352008</t>
+          <t>5551.24813381213</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963778797</t>
+          <t>5915.81755185332</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017002857388</t>
+          <t>6353.9980421919</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182519938</t>
+          <t>6922.83671966773</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926327915</t>
+          <t>6736.17728339617</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431997418625</t>
+          <t>6349.29241576971</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660723050932</t>
+          <t>6036.5789375175</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902078434333</t>
+          <t>5918.53501167592</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948696077396</t>
+          <t>6027.96198710269</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>3568177636.64903</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>3685972670.42053</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1996750008.00658</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>3096311347.63204</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2820657592.27239</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>3676647217.51498</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>4106483185.72538</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>4175938621.03306</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>4292547722.11089</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>4181025514.67538</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>3345467875.79742</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>3613645222.36609</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>4264765453.47415</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>3829372043.50048</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2287993688.45654</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>4331441836.74937</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>4428539901.39528</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>2672672861.10271</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>3905996385.16128</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3431870999.78283</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>4046761237.59855</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>4540458684.15232</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>4475316578.50777</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>4478946798.94981</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>4398316480.73778</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>3604647645.57739</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>3842949150.90538</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>4384027425.04081</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>4065818305.25908</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>2689626431.22769</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-763264200.100343</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>-742567230.97475</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>-675922853.09613</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>-809685037.52924</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>-611213407.510434</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-370114020.083572</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>-433975498.426942</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>-299377957.474709</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>-186399076.838923</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>-217290966.062404</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>-259179769.779969</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>-229303928.539294</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>-119261971.566659</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>-236446261.7586</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-401632742.771158</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>3541.30672623868</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>3505.89628834078</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>3339.08021362511</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>3292.80386232129</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>3446.36941491692</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>3572.31647742793</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>3608.37623699562</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>3622.34439728286</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>3543.79038551462</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>3884.48923067424</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>3890.72730279517</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>3931.21230769383</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3816.95486116527</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3775.57722681653</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>3921.98997115</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>3840.2388085693</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>3774.60108179556</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>3580.01013639576</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>3534.56743468929</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>3695.56428704505</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>3828.77603654616</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>3844.91780476741</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>3858.46300644147</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>3765.55744830244</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>4149.42577792539</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>4158.83868662663</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>4279.03888460161</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>4168.50309270722</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>4107.54568996469</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>4271.92323753344</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>27640.9337524315</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>29019.0193074826</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>28310.2427954189</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>29811.2195315843</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>29866.7838936402</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>29622.0729143587</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>29274.9031269511</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>31937.3752722009</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>39403.3919798719</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>45584.9115575512</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>46689.0464825974</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>55476.3653839372</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>66247.6968135601</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>72611.1153732561</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>56774.3546623424</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>4302338042.95865</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-10.53</t>
+          <t>4077603672.04196</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>3912234000.59468</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>4366840193.5392</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>4501214543.42859</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>5162729226.49203</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>5062391887.49624</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>5051161140.24788</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>5039177731.89831</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-25.3</t>
+          <t>5522664768.58047</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-24.15</t>
+          <t>5277760938.67984</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>5652965200.80534</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>5694496773.89835</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-19.49</t>
+          <t>5848566834.11691</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-20.37</t>
+          <t>3983817520.15787</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-53.39</t>
+          <t>36177.3965766024</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-54.44</t>
+          <t>38006.2865614381</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-54.15</t>
+          <t>37903.7436388389</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-59</t>
+          <t>41710.3672123693</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-57.97</t>
+          <t>43418.0653201364</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-56.39</t>
+          <t>43173.7892041376</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-57.87</t>
+          <t>42744.2509021729</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-60.31</t>
+          <t>44343.7977337756</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-68.2</t>
+          <t>52010.6869567796</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-64.49</t>
+          <t>62850.1014201555</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-63.14</t>
+          <t>66279.3469024905</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>74631.9736788276</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-59.85</t>
+          <t>87100.1523424979</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-59.28</t>
+          <t>100750.894634779</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>77465.8001901647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17399.354</t>
+          <t>11161389002.2558</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17389.587</t>
+          <t>11109273803.6124</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16924.856</t>
+          <t>9244996586.37211</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17178.705</t>
+          <t>12059833650.8518</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18208.045</t>
+          <t>12875540268.828</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19258.743</t>
+          <t>14708736095.2795</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19690.593</t>
+          <t>15344034512.6179</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19876.1</t>
+          <t>14822778329.41</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19287.185</t>
+          <t>14283277766.0201</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21231.782</t>
+          <t>16270705210.273</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21210.077</t>
+          <t>15426761209.5633</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>22254.853</t>
+          <t>15245595699.3702</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>21667.399</t>
+          <t>15426165406.0276</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>21431.597</t>
+          <t>16089842668.272</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>21586.947</t>
+          <t>11550304087.8167</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12663.005</t>
+          <t>-8536.46282417083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12683.982</t>
+          <t>-8987.26725395548</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12433.065</t>
+          <t>-9593.50084341999</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12648.977</t>
+          <t>-11899.1476807851</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13521.486</t>
+          <t>-13551.2814264962</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14296.768</t>
+          <t>-13551.7162897789</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14651.451</t>
+          <t>-13469.3477752218</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14926.547</t>
+          <t>-12406.4224615746</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14483.449</t>
+          <t>-12607.2949769077</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15992.007</t>
+          <t>-17265.1898626044</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16061.311</t>
+          <t>-19590.3004198931</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>17127.506</t>
+          <t>-19155.6082948903</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16698.74</t>
+          <t>-20852.4555289378</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16596.583</t>
+          <t>-28139.7792615227</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16920.483</t>
+          <t>-20691.4455278223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25026.464</t>
+          <t>-6859050959.29717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24396.02</t>
+          <t>-7031670131.57039</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22448.514</t>
+          <t>-5332762585.77744</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>24594.121</t>
+          <t>-7692993457.31255</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>25338.936</t>
+          <t>-8374325725.39939</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28348.91</t>
+          <t>-9546006868.78746</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28633.456</t>
+          <t>-10281642625.1216</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27691.654</t>
+          <t>-9771617189.16211</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26444.07</t>
+          <t>-9244100034.12178</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>29269.044</t>
+          <t>-10748040441.6925</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>28118.264</t>
+          <t>-10149000270.8835</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28295.032</t>
+          <t>-9592630498.5649</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>28217.022</t>
+          <t>-9731668632.1293</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>28422.789</t>
+          <t>-10241275834.1551</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>22826.136</t>
+          <t>-7566486567.65882</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>47261.90014</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>49497.83805</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>46463.78923</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>48461.172</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>48975.98629</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>44954.7972</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>46166.54136</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>50509.3192</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>60343.79544</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>68833.81575</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>69269.37126</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>73877.99624</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>84047.31703</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>91177.72296</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>84332.33482</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9532.104</t>
+          <t>0.0670726849865342</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9451.895</t>
+          <t>0.0618770037455118</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9205.803</t>
+          <t>0.0630103284102806</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9278.371</t>
+          <t>0.0634023739514106</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9683.579</t>
+          <t>0.0629514694420938</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10215.834</t>
+          <t>0.0558547872665729</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10349.016</t>
+          <t>0.056360602009569</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10262.443</t>
+          <t>0.0545500640497308</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>9755.536</t>
+          <t>0.0521983263470341</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10578.22</t>
+          <t>0.0536937649049948</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10394.592</t>
+          <t>0.0467151894374185</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10715.459</t>
+          <t>0.040865785705064</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>10382.214</t>
+          <t>0.0467147927156727</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>10144.956</t>
+          <t>0.0268533997863547</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>10256.324</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>54517.4651070032</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>57330.1530302811</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>55091.0606983683</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>58355.0120387198</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>59941.9741107586</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>56378.2077130772</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>57660.4321514658</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>63999.5308730138</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>78562.5165176056</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>89326.0714626469</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>93752.8850865868</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>100487.676195267</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>113975.170066242</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>126619.355989369</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>119754.25756002</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18760.369</t>
+          <t>64390.1429588036</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19254.2</t>
+          <t>67805.5106716471</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19023.402</t>
+          <t>64867.0389090267</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21388.731</t>
+          <t>68669.0676641218</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21761.231</t>
+          <t>70200.0766136047</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21417.008</t>
+          <t>65915.005808849</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>22540.288</t>
+          <t>67564.8492680654</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24377.232</t>
+          <t>74278.3257723271</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>25968.749</t>
+          <t>91231.3826085677</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>28500.544</t>
+          <t>103177.855088524</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>27807.613</t>
+          <t>107837.011122488</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>27662.597</t>
+          <t>113883.213810508</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>26409.341</t>
+          <t>129523.7389639</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>26016.54</t>
+          <t>143772.790474636</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>26006.193</t>
+          <t>136117.219650223</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-32.5</t>
+          <t>252503.423695737</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-34.12</t>
+          <t>265446.736551503</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-34.64</t>
+          <t>251036.482845167</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-40.86</t>
+          <t>259161.331950268</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>264984.097880274</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-33.25</t>
+          <t>256637.933778636</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>266276.129359737</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>303086.861468923</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-44.23</t>
+          <t>377851.644004267</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-43.89</t>
+          <t>441580.44506998</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>464635.182431894</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-38.08</t>
+          <t>549246.397136294</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>635663.922809273</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-36.21</t>
+          <t>748501.928456876</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4.294</t>
+          <t>64390.1429588036</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>67480.0646625834</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>70320.8775849907</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>73474.7200641347</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>76036.5708261408</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.043</t>
+          <t>79078.0310994742</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>80432.0923275821</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.588</t>
+          <t>81181.8815101035</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>81308.8012167277</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.516</t>
+          <t>81803.2386717955</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.253</t>
+          <t>84540.4046688046</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>84545.2730358901</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.543</t>
+          <t>86104.4154627638</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.339</t>
+          <t>87777.5072634118</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.066</t>
+          <t>85981.5207761966</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>54517.4651070032</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>56826.1434413121</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>59341.7859978765</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>62170.0291181261</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>64303.7549449304</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>67078.8482776295</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>68071.9727332793</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>69068.4448217795</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>69126.7083017543</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>69672.5223214297</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>72063.2419286917</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>72692.9986523384</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>73652.5746550169</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>74940.7497150159</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>73062.7696026812</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>34667.5072411964</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>35040.6421883529</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>33257.5303509733</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34601.5213958782</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>35304.8449163953</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>32489.865801151</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>33474.2392219346</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>37066.7338476729</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>45038.9599514322</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>52695.4953114758</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>51859.1439775121</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>56881.7743194917</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>70155.2290960997</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>75630.3733753642</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>69529.937939777</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12663004591.6843</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>12683982181.5881</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12433065175.4331</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12648976756.721</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>13521485762.485</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>14296767774.3143</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14651450872.697</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14926547237.4844</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14483448590.534</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15992007464.0784</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16061311378.6687</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>17127505782.1605</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16698740148.772</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>16596582590.306</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>16920482692.6067</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>17399353993.8658</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>17389587183.8321</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16924855920.8246</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>17178704646.0769</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>18208045242.271</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>19258743463.8272</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>19690593061.7748</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>19876100485.082</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>19287185250.2051</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>21231781820.4886</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>21210077301.7958</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>22254853334.9245</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>21667398806.7204</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>21431597235.4481</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>21586947223.8636</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9532104010.05766</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9451895257.45487</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9205802962.43903</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9278371017.16703</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9683579005.25829</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10215833504.629</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10349016225.4391</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10262442850.6247</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9755536268.35281</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10578220428.5806</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>10394591710.9577</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>10715459066.2727</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>10382213690.9868</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10144955694.5727</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>10256323580.691</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4530800</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4607000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4727600</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4860200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4927000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5030000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5121200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5151300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5122000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5116800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5100000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5200900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5197884.78617838</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5217616.27334019</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5053215.15007551</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3575800</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3617900</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3723500</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3841400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3923400</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4002100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4060400</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4120686.93652677</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4086993.59017837</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4116888.09375398</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4128100</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4356800</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4374885.41420007</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4395773.57136985</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4314259.55116487</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8693291604.54445</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8720653411.22951</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8753428328.46158</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8907131147.44126</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>9115372875.80184</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9296704880.21882</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9445793656.45739</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9496836440.10518</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9343179090.48792</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9429324368.61149</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9396912528.61733</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9539605679.76632</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>9588835861.71984</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>9552776868.75569</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9196083608.80906</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6769189057.17861</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6753915358.02492</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6802734105.03599</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6949964879.60813</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7170217229.08824</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7306096701.79946</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7399158866.51142</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7507101468.83552</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7368322769.92465</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7502137396.7577</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7523578475.91159</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7933461390.82089</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7984655273.33706</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7978692834.63733</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7814952668.66301</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.238398181075991</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.238066858392622</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.227747502565765</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.222195166027263</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.227510176938149</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.236635290578604</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.237382087297179</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.245302050306835</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.275482376902733</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.28449733732479</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.295094001750916</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.298329438757012</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.301798731469841</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.316575687650561</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.330108019208722</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.257810155388644</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.262483109911152</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.253153617711366</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.247344634029229</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.269763750117847</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.279114814698076</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.28729365765645</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.282124417776103</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.263264598572064</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.280678248137305</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.277918201322617</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.283936834437297</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.270321088442263</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.262729373640372</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.278962492441108</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.503791663535365</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.499450031696226</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.519098879722869</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.530460199943508</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.502726072944004</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.48424989472332</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.475324255046371</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.472573531917062</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.461253024525203</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.434824414537904</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.426987796926467</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.417733726805691</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.427880180087895</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.420694938709067</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.39092948835017</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>213812.0333</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>222990.11506</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>213822.28989</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>223424.66515</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>225367.87645</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>213234.12247</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>218804.7583</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>236466.93974</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>286966.08772</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>331001.15055</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>344211.48461</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>368347.07761</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>430233.16998</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>470095.58823</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>434233.98944</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>99057.6502</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>102846.15286</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>98124.56926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>103270.58906</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>105504.92153</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>98404.87161</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>101039.08849</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>111345.05962</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>136270.34256</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>155873.3504</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>159696.1551</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>170764.98813</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>199678.96806</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>219403.16385</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>205647.15759</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>190168.190462641</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>200355.738959211</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>213535.417764474</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>229806.514114063</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>247992.67951214</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>267016.360227936</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>286126.853802035</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>302964.105787775</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>316888.833360764</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>330794.34786892</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>343547.434089003</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>358085.796585842</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>372452.561789273</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>385641.498958623</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
